--- a/files/Aufmaß_Montage.xlsx
+++ b/files/Aufmaß_Montage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\P-IT\EPA\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A10824-4F74-465A-860E-6C0E8F57AFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84204FF0-7588-4F65-8E8F-04015D0029B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufmaß" sheetId="1" r:id="rId1"/>
